--- a/output/pdf_financials_xlsx/EAGR.xlsx
+++ b/output/pdf_financials_xlsx/EAGR.xlsx
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.05977</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>1.312366</v>
@@ -10834,7 +10834,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EAGR.xlsx
+++ b/output/pdf_financials_xlsx/EAGR.xlsx
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.032598</v>
@@ -1496,7 +1496,7 @@
         <v>7.554463</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.347948</v>
       </c>
     </row>
     <row r="35">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.032598</v>
@@ -1558,7 +1558,7 @@
         <v>7.554463</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.347948</v>
       </c>
     </row>
     <row r="37">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>1.25</v>
@@ -1930,7 +1930,7 @@
         <v>6.301689</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.948443</v>
+        <v>5.600495</v>
       </c>
     </row>
     <row r="49">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">

--- a/output/pdf_financials_xlsx/EAGR.xlsx
+++ b/output/pdf_financials_xlsx/EAGR.xlsx
@@ -1314,19 +1314,19 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.398028</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.336432</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.180708</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.142392</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.129002</v>
       </c>
     </row>
     <row r="29">
@@ -1345,19 +1345,19 @@
         <v>20.142836</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.080937</v>
+        <v>-2.682909</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.954162</v>
+        <v>10.290594</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.281406</v>
+        <v>-0.100698</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.69006</v>
+        <v>-0.547668</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-22.173022</v>
+        <v>-22.04402</v>
       </c>
     </row>
     <row r="30">
@@ -1380,19 +1380,19 @@
         <v>29.59985672982535</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3.306194015552714</v>
+        <v>-2.87906493384075</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.560538885150629</v>
+        <v>8.849869038528583</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.3235363354082791</v>
+        <v>-0.1157738708589827</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-0.8302225553731952</v>
+        <v>-0.6589083941340276</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-28.58109977946828</v>
+        <v>-28.41481576848633</v>
       </c>
     </row>
     <row r="31">
@@ -3633,16 +3633,16 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.336432</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.180708</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.142392</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.129002</v>
       </c>
     </row>
     <row r="101">
@@ -11286,7 +11286,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -13334,7 +13338,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -15708,7 +15716,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -16940,7 +16952,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -17438,7 +17454,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EAGR.xlsx
+++ b/output/pdf_financials_xlsx/EAGR.xlsx
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.02523</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2645,13 +2645,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.17439</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.17439</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.131201</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0</v>
@@ -2676,13 +2676,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.17439</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.17439</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.131201</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3.93718</v>
+        <v>3.76279</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>3.02131</v>
+        <v>2.84692</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.87</v>
+        <v>0.738799</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -2962,20 +2962,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.006799486235046608</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.006519122441410794</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.002703998488740168</v>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
@@ -4018,16 +4012,16 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.270038</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.084676</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.075502</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.093297</v>
       </c>
     </row>
     <row r="112">
@@ -4837,16 +4831,16 @@
         </is>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.270038</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.084676</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.075502</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.093297</v>
       </c>
     </row>
     <row r="135">
@@ -4874,16 +4868,16 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>10.091003</v>
+        <v>9.820964999999999</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>1.572994</v>
+        <v>1.488318</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>7.295689</v>
+        <v>7.220187</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.632331</v>
+        <v>-3.725628</v>
       </c>
     </row>
   </sheetData>
@@ -8142,7 +8136,11 @@
           <t>Current portion of lease obligation -</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -9452,7 +9450,11 @@
           <t>Current portion of lease obligation 16</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -11946,7 +11948,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -12836,7 +12842,11 @@
           <t>Purchase of equipment 7 $</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -14068,7 +14078,11 @@
           <t>Purchase of equipment $</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -19238,7 +19252,11 @@
           <t>Deferred income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
